--- a/SwissTechSaqib/Swiss Tech Files 2025/Ledgers 2025/Fedex Labels/FedEx Labels Report May 2026.xlsx
+++ b/SwissTechSaqib/Swiss Tech Files 2025/Ledgers 2025/Fedex Labels/FedEx Labels Report May 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D Drive Tipu\Swiss Tech Global\02 Swiss Tech LLC USA\04 FedEx\03 Labels reports for Accounts Department\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\SwissTechSaqib\Swiss Tech Files 2025\Ledgers 2025\Fedex Labels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C334BFAA-BD9C-4571-ACB1-EB9348A28B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED94E17-1A16-4FA6-8457-22A5701F90BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Swiss Tech LLC Labels" sheetId="7" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
   <si>
     <t>Shipping Label</t>
   </si>
@@ -746,10 +746,21 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="1"/>
+      <c r="A5" s="3">
+        <v>46172</v>
+      </c>
+      <c r="B5" s="2">
+        <v>872432225224</v>
+      </c>
+      <c r="C5" s="7">
+        <v>196.57</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
